--- a/template/Static_ExcelReport.xlsx
+++ b/template/Static_ExcelReport.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\DoPENet_Connect\bin\x64\Debug\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC534E99-B9B8-4B74-B122-AFC9071B408B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91C833A-46BF-43A1-8CB3-83F4EDB931FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="试验报告" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">试验报告!$A$1:$H$114</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -26,10 +29,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>试验报告</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
   <si>
     <t>试样编号：</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -75,6 +74,10 @@
   <si>
     <t>2025-09-11 02:30:18</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">                             试验报告</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -158,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -220,11 +223,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -512,7 +521,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:I39"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:W139"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.625" style="18" customWidth="1"/>
@@ -1030,26 +1042,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
-        <v>0</v>
+      <c r="A2" s="25" t="s">
+        <v>9</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:9" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="24"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
@@ -1063,34 +1075,34 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="25"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
+      <c r="A6" s="27"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
       <c r="I6" s="6"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -1106,7 +1118,7 @@
     </row>
     <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="8"/>
@@ -1129,309 +1141,1088 @@
       <c r="I9" s="13"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="26"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
       <c r="I10" s="13"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="26"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
       <c r="I11" s="17"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="26"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
       <c r="I12" s="17"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="26"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
       <c r="I13" s="17"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="26"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
       <c r="I14" s="17"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="26"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
       <c r="I15" s="17"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="26"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
       <c r="I16" s="17"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" s="26"/>
-      <c r="B17" s="26"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
       <c r="I17" s="17"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" s="26"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
       <c r="I18" s="17"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" s="26"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
       <c r="I19" s="17"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="26"/>
-      <c r="B20" s="26"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
       <c r="I20" s="17"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21" s="26"/>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
+      <c r="A21" s="28"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
       <c r="I21" s="17"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" s="26"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
+      <c r="A22" s="28"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
       <c r="I22" s="17"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" s="26"/>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
+      <c r="A23" s="28"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
       <c r="I23" s="17"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="26"/>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
+      <c r="A24" s="28"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
       <c r="I24" s="17"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" s="26"/>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
+      <c r="A25" s="28"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
       <c r="I25" s="17"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" s="26"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
+      <c r="A26" s="28"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
       <c r="I26" s="17"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" s="26"/>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
+      <c r="A27" s="28"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
       <c r="I27" s="17"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="26"/>
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
+      <c r="A28" s="28"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
       <c r="I28" s="17"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29" s="26"/>
-      <c r="B29" s="26"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
+      <c r="A29" s="28"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
       <c r="I29" s="17"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" s="26"/>
-      <c r="B30" s="26"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
+      <c r="A30" s="28"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" s="26"/>
-      <c r="B31" s="26"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
+      <c r="A31" s="28"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" s="26"/>
-      <c r="B32" s="26"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
+      <c r="A32" s="28"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="26"/>
-      <c r="B33" s="26"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
+      <c r="A33" s="28"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="26"/>
-      <c r="B34" s="26"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-    </row>
-    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="24"/>
-      <c r="B35" s="24"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="24"/>
+      <c r="A34" s="28"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="24"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="24"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="24"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="24"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="24"/>
+      <c r="B38" s="24"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
+      <c r="H38" s="24"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B39" s="19" t="s">
+      <c r="A39" s="24"/>
+      <c r="B39" s="24"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="24"/>
+      <c r="H39" s="24"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="24"/>
+      <c r="B40" s="24"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="24"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="24"/>
+      <c r="B41" s="24"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
+      <c r="H41" s="24"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42" s="24"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" s="24"/>
+      <c r="B43" s="24"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="24"/>
+      <c r="H43" s="24"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" s="24"/>
+      <c r="B44" s="24"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="24"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="24"/>
+      <c r="H44" s="24"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" s="24"/>
+      <c r="B45" s="24"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="24"/>
+      <c r="H45" s="24"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" s="24"/>
+      <c r="B46" s="24"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
+      <c r="H46" s="24"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" s="24"/>
+      <c r="B47" s="24"/>
+      <c r="C47" s="24"/>
+      <c r="D47" s="24"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="24"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" s="24"/>
+      <c r="B48" s="24"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="24"/>
+      <c r="H48" s="24"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A49" s="24"/>
+      <c r="B49" s="24"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="24"/>
+      <c r="H49" s="24"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A50" s="24"/>
+      <c r="B50" s="24"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="24"/>
+      <c r="E50" s="24"/>
+      <c r="F50" s="24"/>
+      <c r="G50" s="24"/>
+      <c r="H50" s="24"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51" s="24"/>
+      <c r="B51" s="24"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="24"/>
+      <c r="G51" s="24"/>
+      <c r="H51" s="24"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52" s="24"/>
+      <c r="B52" s="24"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="24"/>
+      <c r="E52" s="24"/>
+      <c r="F52" s="24"/>
+      <c r="G52" s="24"/>
+      <c r="H52" s="24"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53" s="24"/>
+      <c r="B53" s="24"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="24"/>
+      <c r="E53" s="24"/>
+      <c r="F53" s="24"/>
+      <c r="G53" s="24"/>
+      <c r="H53" s="24"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A54" s="24"/>
+      <c r="B54" s="24"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="24"/>
+      <c r="F54" s="24"/>
+      <c r="G54" s="24"/>
+      <c r="H54" s="24"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A55" s="24"/>
+      <c r="B55" s="24"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="24"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A56" s="24"/>
+      <c r="B56" s="24"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="24"/>
+      <c r="E56" s="24"/>
+      <c r="F56" s="24"/>
+      <c r="G56" s="24"/>
+      <c r="H56" s="24"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A57" s="24"/>
+      <c r="B57" s="24"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="24"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="24"/>
+      <c r="G57" s="24"/>
+      <c r="H57" s="24"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A58" s="24"/>
+      <c r="B58" s="24"/>
+      <c r="C58" s="24"/>
+      <c r="D58" s="24"/>
+      <c r="E58" s="24"/>
+      <c r="F58" s="24"/>
+      <c r="G58" s="24"/>
+      <c r="H58" s="24"/>
+    </row>
+    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="24"/>
+      <c r="B59" s="24"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="24"/>
+      <c r="F59" s="24"/>
+      <c r="G59" s="24"/>
+      <c r="H59" s="24"/>
+    </row>
+    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="17"/>
+      <c r="B60" s="17"/>
+      <c r="C60" s="17"/>
+      <c r="D60" s="17"/>
+      <c r="E60" s="17"/>
+      <c r="F60" s="17"/>
+      <c r="G60" s="17"/>
+      <c r="H60" s="17"/>
+    </row>
+    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="24"/>
+      <c r="B61" s="24"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+    </row>
+    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="24"/>
+      <c r="B62" s="24"/>
+      <c r="C62" s="24"/>
+      <c r="D62" s="24"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="24"/>
+      <c r="H62" s="24"/>
+    </row>
+    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="24"/>
+      <c r="B63" s="24"/>
+      <c r="C63" s="24"/>
+      <c r="D63" s="24"/>
+      <c r="E63" s="24"/>
+      <c r="F63" s="24"/>
+      <c r="G63" s="24"/>
+      <c r="H63" s="24"/>
+    </row>
+    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="24"/>
+      <c r="B64" s="24"/>
+      <c r="C64" s="24"/>
+      <c r="D64" s="24"/>
+      <c r="E64" s="24"/>
+      <c r="F64" s="24"/>
+      <c r="G64" s="24"/>
+      <c r="H64" s="24"/>
+    </row>
+    <row r="65" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="24"/>
+      <c r="B65" s="24"/>
+      <c r="C65" s="24"/>
+      <c r="D65" s="24"/>
+      <c r="E65" s="24"/>
+      <c r="F65" s="24"/>
+      <c r="G65" s="24"/>
+      <c r="H65" s="24"/>
+    </row>
+    <row r="66" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="24"/>
+      <c r="B66" s="24"/>
+      <c r="C66" s="24"/>
+      <c r="D66" s="24"/>
+      <c r="E66" s="24"/>
+      <c r="F66" s="24"/>
+      <c r="G66" s="24"/>
+      <c r="H66" s="24"/>
+    </row>
+    <row r="67" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="24"/>
+      <c r="B67" s="24"/>
+      <c r="C67" s="24"/>
+      <c r="D67" s="24"/>
+      <c r="E67" s="24"/>
+      <c r="F67" s="24"/>
+      <c r="G67" s="24"/>
+      <c r="H67" s="24"/>
+    </row>
+    <row r="68" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="24"/>
+      <c r="B68" s="24"/>
+      <c r="C68" s="24"/>
+      <c r="D68" s="24"/>
+      <c r="E68" s="24"/>
+      <c r="F68" s="24"/>
+      <c r="G68" s="24"/>
+      <c r="H68" s="24"/>
+    </row>
+    <row r="69" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="24"/>
+      <c r="B69" s="24"/>
+      <c r="C69" s="24"/>
+      <c r="D69" s="24"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
+      <c r="H69" s="24"/>
+    </row>
+    <row r="70" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="24"/>
+      <c r="B70" s="24"/>
+      <c r="C70" s="24"/>
+      <c r="D70" s="24"/>
+      <c r="E70" s="24"/>
+      <c r="F70" s="24"/>
+      <c r="G70" s="24"/>
+      <c r="H70" s="24"/>
+    </row>
+    <row r="71" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="24"/>
+      <c r="B71" s="24"/>
+      <c r="C71" s="24"/>
+      <c r="D71" s="24"/>
+      <c r="E71" s="24"/>
+      <c r="F71" s="24"/>
+      <c r="G71" s="24"/>
+      <c r="H71" s="24"/>
+    </row>
+    <row r="72" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="24"/>
+      <c r="B72" s="24"/>
+      <c r="C72" s="24"/>
+      <c r="D72" s="24"/>
+      <c r="E72" s="24"/>
+      <c r="F72" s="24"/>
+      <c r="G72" s="24"/>
+      <c r="H72" s="24"/>
+    </row>
+    <row r="73" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="24"/>
+      <c r="B73" s="24"/>
+      <c r="C73" s="24"/>
+      <c r="D73" s="24"/>
+      <c r="E73" s="24"/>
+      <c r="F73" s="24"/>
+      <c r="G73" s="24"/>
+      <c r="H73" s="24"/>
+    </row>
+    <row r="74" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="24"/>
+      <c r="B74" s="24"/>
+      <c r="C74" s="24"/>
+      <c r="D74" s="24"/>
+      <c r="E74" s="24"/>
+      <c r="F74" s="24"/>
+      <c r="G74" s="24"/>
+      <c r="H74" s="24"/>
+    </row>
+    <row r="75" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="24"/>
+      <c r="B75" s="24"/>
+      <c r="C75" s="24"/>
+      <c r="D75" s="24"/>
+      <c r="E75" s="24"/>
+      <c r="F75" s="24"/>
+      <c r="G75" s="24"/>
+      <c r="H75" s="24"/>
+    </row>
+    <row r="76" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="24"/>
+      <c r="B76" s="24"/>
+      <c r="C76" s="24"/>
+      <c r="D76" s="24"/>
+      <c r="E76" s="24"/>
+      <c r="F76" s="24"/>
+      <c r="G76" s="24"/>
+      <c r="H76" s="24"/>
+    </row>
+    <row r="77" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="24"/>
+      <c r="B77" s="24"/>
+      <c r="C77" s="24"/>
+      <c r="D77" s="24"/>
+      <c r="E77" s="24"/>
+      <c r="F77" s="24"/>
+      <c r="G77" s="24"/>
+      <c r="H77" s="24"/>
+    </row>
+    <row r="78" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="24"/>
+      <c r="B78" s="24"/>
+      <c r="C78" s="24"/>
+      <c r="D78" s="24"/>
+      <c r="E78" s="24"/>
+      <c r="F78" s="24"/>
+      <c r="G78" s="24"/>
+      <c r="H78" s="24"/>
+    </row>
+    <row r="79" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="24"/>
+      <c r="B79" s="24"/>
+      <c r="C79" s="24"/>
+      <c r="D79" s="24"/>
+      <c r="E79" s="24"/>
+      <c r="F79" s="24"/>
+      <c r="G79" s="24"/>
+      <c r="H79" s="24"/>
+    </row>
+    <row r="80" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="24"/>
+      <c r="B80" s="24"/>
+      <c r="C80" s="24"/>
+      <c r="D80" s="24"/>
+      <c r="E80" s="24"/>
+      <c r="F80" s="24"/>
+      <c r="G80" s="24"/>
+      <c r="H80" s="24"/>
+    </row>
+    <row r="81" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="24"/>
+      <c r="B81" s="24"/>
+      <c r="C81" s="24"/>
+      <c r="D81" s="24"/>
+      <c r="E81" s="24"/>
+      <c r="F81" s="24"/>
+      <c r="G81" s="24"/>
+      <c r="H81" s="24"/>
+    </row>
+    <row r="82" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="24"/>
+      <c r="B82" s="24"/>
+      <c r="C82" s="24"/>
+      <c r="D82" s="24"/>
+      <c r="E82" s="24"/>
+      <c r="F82" s="24"/>
+      <c r="G82" s="24"/>
+      <c r="H82" s="24"/>
+    </row>
+    <row r="83" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="24"/>
+      <c r="B83" s="24"/>
+      <c r="C83" s="24"/>
+      <c r="D83" s="24"/>
+      <c r="E83" s="24"/>
+      <c r="F83" s="24"/>
+      <c r="G83" s="24"/>
+      <c r="H83" s="24"/>
+    </row>
+    <row r="84" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="24"/>
+      <c r="B84" s="24"/>
+      <c r="C84" s="24"/>
+      <c r="D84" s="24"/>
+      <c r="E84" s="24"/>
+      <c r="F84" s="24"/>
+      <c r="G84" s="24"/>
+      <c r="H84" s="24"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A85" s="24"/>
+      <c r="B85" s="24"/>
+      <c r="C85" s="24"/>
+      <c r="D85" s="24"/>
+      <c r="E85" s="24"/>
+      <c r="F85" s="24"/>
+      <c r="G85" s="24"/>
+      <c r="H85" s="24"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A86" s="17"/>
+      <c r="B86" s="17"/>
+      <c r="C86" s="17"/>
+      <c r="D86" s="17"/>
+      <c r="E86" s="17"/>
+      <c r="F86" s="17"/>
+      <c r="G86" s="17"/>
+      <c r="H86" s="17"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A87" s="24"/>
+      <c r="B87" s="24"/>
+      <c r="C87" s="24"/>
+      <c r="D87" s="24"/>
+      <c r="E87" s="24"/>
+      <c r="F87" s="24"/>
+      <c r="G87" s="24"/>
+      <c r="H87" s="24"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A88" s="24"/>
+      <c r="B88" s="24"/>
+      <c r="C88" s="24"/>
+      <c r="D88" s="24"/>
+      <c r="E88" s="24"/>
+      <c r="F88" s="24"/>
+      <c r="G88" s="24"/>
+      <c r="H88" s="24"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A89" s="24"/>
+      <c r="B89" s="24"/>
+      <c r="C89" s="24"/>
+      <c r="D89" s="24"/>
+      <c r="E89" s="24"/>
+      <c r="F89" s="24"/>
+      <c r="G89" s="24"/>
+      <c r="H89" s="24"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A90" s="24"/>
+      <c r="B90" s="24"/>
+      <c r="C90" s="24"/>
+      <c r="D90" s="24"/>
+      <c r="E90" s="24"/>
+      <c r="F90" s="24"/>
+      <c r="G90" s="24"/>
+      <c r="H90" s="24"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A91" s="24"/>
+      <c r="B91" s="24"/>
+      <c r="C91" s="24"/>
+      <c r="D91" s="24"/>
+      <c r="E91" s="24"/>
+      <c r="F91" s="24"/>
+      <c r="G91" s="24"/>
+      <c r="H91" s="24"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A92" s="24"/>
+      <c r="B92" s="24"/>
+      <c r="C92" s="24"/>
+      <c r="D92" s="24"/>
+      <c r="E92" s="24"/>
+      <c r="F92" s="24"/>
+      <c r="G92" s="24"/>
+      <c r="H92" s="24"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A93" s="24"/>
+      <c r="B93" s="24"/>
+      <c r="C93" s="24"/>
+      <c r="D93" s="24"/>
+      <c r="E93" s="24"/>
+      <c r="F93" s="24"/>
+      <c r="G93" s="24"/>
+      <c r="H93" s="24"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A94" s="24"/>
+      <c r="B94" s="24"/>
+      <c r="C94" s="24"/>
+      <c r="D94" s="24"/>
+      <c r="E94" s="24"/>
+      <c r="F94" s="24"/>
+      <c r="G94" s="24"/>
+      <c r="H94" s="24"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A95" s="24"/>
+      <c r="B95" s="24"/>
+      <c r="C95" s="24"/>
+      <c r="D95" s="24"/>
+      <c r="E95" s="24"/>
+      <c r="F95" s="24"/>
+      <c r="G95" s="24"/>
+      <c r="H95" s="24"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A96" s="24"/>
+      <c r="B96" s="24"/>
+      <c r="C96" s="24"/>
+      <c r="D96" s="24"/>
+      <c r="E96" s="24"/>
+      <c r="F96" s="24"/>
+      <c r="G96" s="24"/>
+      <c r="H96" s="24"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A97" s="24"/>
+      <c r="B97" s="24"/>
+      <c r="C97" s="24"/>
+      <c r="D97" s="24"/>
+      <c r="E97" s="24"/>
+      <c r="F97" s="24"/>
+      <c r="G97" s="24"/>
+      <c r="H97" s="24"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A98" s="24"/>
+      <c r="B98" s="24"/>
+      <c r="C98" s="24"/>
+      <c r="D98" s="24"/>
+      <c r="E98" s="24"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="24"/>
+      <c r="H98" s="24"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A99" s="24"/>
+      <c r="B99" s="24"/>
+      <c r="C99" s="24"/>
+      <c r="D99" s="24"/>
+      <c r="E99" s="24"/>
+      <c r="F99" s="24"/>
+      <c r="G99" s="24"/>
+      <c r="H99" s="24"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A100" s="24"/>
+      <c r="B100" s="24"/>
+      <c r="C100" s="24"/>
+      <c r="D100" s="24"/>
+      <c r="E100" s="24"/>
+      <c r="F100" s="24"/>
+      <c r="G100" s="24"/>
+      <c r="H100" s="24"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A101" s="24"/>
+      <c r="B101" s="24"/>
+      <c r="C101" s="24"/>
+      <c r="D101" s="24"/>
+      <c r="E101" s="24"/>
+      <c r="F101" s="24"/>
+      <c r="G101" s="24"/>
+      <c r="H101" s="24"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A102" s="24"/>
+      <c r="B102" s="24"/>
+      <c r="C102" s="24"/>
+      <c r="D102" s="24"/>
+      <c r="E102" s="24"/>
+      <c r="F102" s="24"/>
+      <c r="G102" s="24"/>
+      <c r="H102" s="24"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A103" s="24"/>
+      <c r="B103" s="24"/>
+      <c r="C103" s="24"/>
+      <c r="D103" s="24"/>
+      <c r="E103" s="24"/>
+      <c r="F103" s="24"/>
+      <c r="G103" s="24"/>
+      <c r="H103" s="24"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A104" s="24"/>
+      <c r="B104" s="24"/>
+      <c r="C104" s="24"/>
+      <c r="D104" s="24"/>
+      <c r="E104" s="24"/>
+      <c r="F104" s="24"/>
+      <c r="G104" s="24"/>
+      <c r="H104" s="24"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A105" s="24"/>
+      <c r="B105" s="24"/>
+      <c r="C105" s="24"/>
+      <c r="D105" s="24"/>
+      <c r="E105" s="24"/>
+      <c r="F105" s="24"/>
+      <c r="G105" s="24"/>
+      <c r="H105" s="24"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A106" s="24"/>
+      <c r="B106" s="24"/>
+      <c r="C106" s="24"/>
+      <c r="D106" s="24"/>
+      <c r="E106" s="24"/>
+      <c r="F106" s="24"/>
+      <c r="G106" s="24"/>
+      <c r="H106" s="24"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A107" s="24"/>
+      <c r="B107" s="24"/>
+      <c r="C107" s="24"/>
+      <c r="D107" s="24"/>
+      <c r="E107" s="24"/>
+      <c r="F107" s="24"/>
+      <c r="G107" s="24"/>
+      <c r="H107" s="24"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A108" s="24"/>
+      <c r="B108" s="24"/>
+      <c r="C108" s="24"/>
+      <c r="D108" s="24"/>
+      <c r="E108" s="24"/>
+      <c r="F108" s="24"/>
+      <c r="G108" s="24"/>
+      <c r="H108" s="24"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A109" s="24"/>
+      <c r="B109" s="24"/>
+      <c r="C109" s="24"/>
+      <c r="D109" s="24"/>
+      <c r="E109" s="24"/>
+      <c r="F109" s="24"/>
+      <c r="G109" s="24"/>
+      <c r="H109" s="24"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A110" s="24"/>
+      <c r="B110" s="24"/>
+      <c r="C110" s="24"/>
+      <c r="D110" s="24"/>
+      <c r="E110" s="24"/>
+      <c r="F110" s="24"/>
+      <c r="G110" s="24"/>
+      <c r="H110" s="24"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A111" s="24"/>
+      <c r="B111" s="24"/>
+      <c r="C111" s="24"/>
+      <c r="D111" s="24"/>
+      <c r="E111" s="24"/>
+      <c r="F111" s="24"/>
+      <c r="G111" s="24"/>
+      <c r="H111" s="24"/>
+    </row>
+    <row r="112" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="23"/>
+      <c r="B112" s="23"/>
+      <c r="C112" s="23"/>
+      <c r="D112" s="23"/>
+      <c r="E112" s="23"/>
+      <c r="F112" s="23"/>
+      <c r="G112" s="23"/>
+      <c r="H112" s="23"/>
+    </row>
+    <row r="114" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C114" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D114" s="20"/>
+      <c r="E114" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C39" s="20"/>
-      <c r="D39" s="19" t="s">
+      <c r="F114" s="21"/>
+      <c r="G114" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="E39" s="21"/>
-      <c r="F39" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="G39" s="22"/>
+      <c r="H114" s="22"/>
+    </row>
+    <row r="139" spans="17:23" x14ac:dyDescent="0.2">
+      <c r="Q139" s="18"/>
+      <c r="S139" s="18"/>
+      <c r="V139" s="18"/>
+      <c r="W139" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="8">
+    <mergeCell ref="A112:H112"/>
+    <mergeCell ref="A36:H59"/>
+    <mergeCell ref="A61:H85"/>
+    <mergeCell ref="A87:H111"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A10:H34"/>
-    <mergeCell ref="A35:H35"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="88" fitToHeight="2" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/template/Static_ExcelReport.xlsx
+++ b/template/Static_ExcelReport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\DoPENet_Connect\bin\x64\Debug\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91C833A-46BF-43A1-8CB3-83F4EDB931FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B48BE357-12F5-4702-9284-B5A38BECB5D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="试验报告" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">试验报告!$A$1:$H$114</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">试验报告!$A$1:$H$37</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -223,12 +223,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -241,6 +235,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1042,26 +1038,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:9" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
+      <c r="A3" s="24"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
@@ -1095,14 +1091,14 @@
       <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="27"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
+      <c r="A6" s="25"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
       <c r="I6" s="6"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -1129,7 +1125,7 @@
       <c r="H8" s="12"/>
       <c r="I8" s="13"/>
     </row>
-    <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="14"/>
       <c r="B9" s="15"/>
       <c r="C9" s="14"/>
@@ -1141,524 +1137,518 @@
       <c r="I9" s="13"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="28"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
+      <c r="A10" s="26"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
       <c r="I10" s="13"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="28"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
+      <c r="A11" s="26"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
       <c r="I11" s="17"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="28"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
+      <c r="A12" s="26"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
       <c r="I12" s="17"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
+      <c r="A13" s="26"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
       <c r="I13" s="17"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="28"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
+      <c r="A14" s="26"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
       <c r="I14" s="17"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="28"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
+      <c r="A15" s="26"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
       <c r="I15" s="17"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="28"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="A16" s="26"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
       <c r="I16" s="17"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" s="28"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
+      <c r="A17" s="26"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
       <c r="I17" s="17"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" s="28"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
+      <c r="A18" s="26"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
       <c r="I18" s="17"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" s="28"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
+      <c r="A19" s="26"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
       <c r="I19" s="17"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="28"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
+      <c r="A20" s="26"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
       <c r="I20" s="17"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21" s="28"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
+      <c r="A21" s="26"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
       <c r="I21" s="17"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" s="28"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
+      <c r="A22" s="26"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
       <c r="I22" s="17"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" s="28"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
+      <c r="A23" s="26"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
       <c r="I23" s="17"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="28"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
+      <c r="A24" s="26"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
       <c r="I24" s="17"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" s="28"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
+      <c r="A25" s="26"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
       <c r="I25" s="17"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" s="28"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
+      <c r="A26" s="26"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
       <c r="I26" s="17"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" s="28"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
+      <c r="A27" s="26"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
       <c r="I27" s="17"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="28"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
+      <c r="A28" s="26"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
       <c r="I28" s="17"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29" s="28"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
+      <c r="A29" s="26"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
       <c r="I29" s="17"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" s="28"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
+      <c r="A30" s="26"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" s="28"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
+      <c r="A31" s="26"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" s="28"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="A32" s="26"/>
+      <c r="B32" s="26"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="28"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
+      <c r="A33" s="26"/>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="28"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="24"/>
-      <c r="B36" s="24"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="24"/>
-      <c r="G36" s="24"/>
-      <c r="H36" s="24"/>
+      <c r="A34" s="26"/>
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="26"/>
+    </row>
+    <row r="35" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="28"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="24"/>
-      <c r="B37" s="24"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="24"/>
+      <c r="C37" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="20"/>
+      <c r="E37" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F37" s="21"/>
+      <c r="G37" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="H37" s="22"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="24"/>
-      <c r="B38" s="24"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="24"/>
-      <c r="H38" s="24"/>
+      <c r="A38" s="27"/>
+      <c r="B38" s="27"/>
+      <c r="C38" s="27"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="27"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="24"/>
-      <c r="B39" s="24"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="24"/>
+      <c r="A39" s="27"/>
+      <c r="B39" s="27"/>
+      <c r="C39" s="27"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="27"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="24"/>
-      <c r="B40" s="24"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="24"/>
+      <c r="A40" s="27"/>
+      <c r="B40" s="27"/>
+      <c r="C40" s="27"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="24"/>
-      <c r="B41" s="24"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="24"/>
+      <c r="A41" s="27"/>
+      <c r="B41" s="27"/>
+      <c r="C41" s="27"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="27"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="24"/>
-      <c r="B42" s="24"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
+      <c r="A42" s="27"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="27"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="24"/>
-      <c r="B43" s="24"/>
-      <c r="C43" s="24"/>
-      <c r="D43" s="24"/>
-      <c r="E43" s="24"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="24"/>
-      <c r="H43" s="24"/>
+      <c r="A43" s="27"/>
+      <c r="B43" s="27"/>
+      <c r="C43" s="27"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="27"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="24"/>
-      <c r="B44" s="24"/>
-      <c r="C44" s="24"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="24"/>
-      <c r="H44" s="24"/>
+      <c r="A44" s="27"/>
+      <c r="B44" s="27"/>
+      <c r="C44" s="27"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="27"/>
+      <c r="H44" s="27"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" s="24"/>
-      <c r="B45" s="24"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="24"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="24"/>
-      <c r="G45" s="24"/>
-      <c r="H45" s="24"/>
+      <c r="A45" s="27"/>
+      <c r="B45" s="27"/>
+      <c r="C45" s="27"/>
+      <c r="D45" s="27"/>
+      <c r="E45" s="27"/>
+      <c r="F45" s="27"/>
+      <c r="G45" s="27"/>
+      <c r="H45" s="27"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="24"/>
-      <c r="B46" s="24"/>
-      <c r="C46" s="24"/>
-      <c r="D46" s="24"/>
-      <c r="E46" s="24"/>
-      <c r="F46" s="24"/>
-      <c r="G46" s="24"/>
-      <c r="H46" s="24"/>
+      <c r="A46" s="27"/>
+      <c r="B46" s="27"/>
+      <c r="C46" s="27"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="27"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" s="24"/>
-      <c r="B47" s="24"/>
-      <c r="C47" s="24"/>
-      <c r="D47" s="24"/>
-      <c r="E47" s="24"/>
-      <c r="F47" s="24"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="24"/>
+      <c r="A47" s="27"/>
+      <c r="B47" s="27"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="27"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="27"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" s="24"/>
-      <c r="B48" s="24"/>
-      <c r="C48" s="24"/>
-      <c r="D48" s="24"/>
-      <c r="E48" s="24"/>
-      <c r="F48" s="24"/>
-      <c r="G48" s="24"/>
-      <c r="H48" s="24"/>
+      <c r="A48" s="27"/>
+      <c r="B48" s="27"/>
+      <c r="C48" s="27"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="27"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="27"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="24"/>
-      <c r="B49" s="24"/>
-      <c r="C49" s="24"/>
-      <c r="D49" s="24"/>
-      <c r="E49" s="24"/>
-      <c r="F49" s="24"/>
-      <c r="G49" s="24"/>
-      <c r="H49" s="24"/>
+      <c r="A49" s="27"/>
+      <c r="B49" s="27"/>
+      <c r="C49" s="27"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="27"/>
+      <c r="H49" s="27"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" s="24"/>
-      <c r="B50" s="24"/>
-      <c r="C50" s="24"/>
-      <c r="D50" s="24"/>
-      <c r="E50" s="24"/>
-      <c r="F50" s="24"/>
-      <c r="G50" s="24"/>
-      <c r="H50" s="24"/>
+      <c r="A50" s="27"/>
+      <c r="B50" s="27"/>
+      <c r="C50" s="27"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="27"/>
+      <c r="G50" s="27"/>
+      <c r="H50" s="27"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" s="24"/>
-      <c r="B51" s="24"/>
-      <c r="C51" s="24"/>
-      <c r="D51" s="24"/>
-      <c r="E51" s="24"/>
-      <c r="F51" s="24"/>
-      <c r="G51" s="24"/>
-      <c r="H51" s="24"/>
+      <c r="A51" s="27"/>
+      <c r="B51" s="27"/>
+      <c r="C51" s="27"/>
+      <c r="D51" s="27"/>
+      <c r="E51" s="27"/>
+      <c r="F51" s="27"/>
+      <c r="G51" s="27"/>
+      <c r="H51" s="27"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52" s="24"/>
-      <c r="B52" s="24"/>
-      <c r="C52" s="24"/>
-      <c r="D52" s="24"/>
-      <c r="E52" s="24"/>
-      <c r="F52" s="24"/>
-      <c r="G52" s="24"/>
-      <c r="H52" s="24"/>
+      <c r="A52" s="27"/>
+      <c r="B52" s="27"/>
+      <c r="C52" s="27"/>
+      <c r="D52" s="27"/>
+      <c r="E52" s="27"/>
+      <c r="F52" s="27"/>
+      <c r="G52" s="27"/>
+      <c r="H52" s="27"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A53" s="24"/>
-      <c r="B53" s="24"/>
-      <c r="C53" s="24"/>
-      <c r="D53" s="24"/>
-      <c r="E53" s="24"/>
-      <c r="F53" s="24"/>
-      <c r="G53" s="24"/>
-      <c r="H53" s="24"/>
+      <c r="A53" s="27"/>
+      <c r="B53" s="27"/>
+      <c r="C53" s="27"/>
+      <c r="D53" s="27"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="27"/>
+      <c r="G53" s="27"/>
+      <c r="H53" s="27"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54" s="24"/>
-      <c r="B54" s="24"/>
-      <c r="C54" s="24"/>
-      <c r="D54" s="24"/>
-      <c r="E54" s="24"/>
-      <c r="F54" s="24"/>
-      <c r="G54" s="24"/>
-      <c r="H54" s="24"/>
+      <c r="A54" s="27"/>
+      <c r="B54" s="27"/>
+      <c r="C54" s="27"/>
+      <c r="D54" s="27"/>
+      <c r="E54" s="27"/>
+      <c r="F54" s="27"/>
+      <c r="G54" s="27"/>
+      <c r="H54" s="27"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A55" s="24"/>
-      <c r="B55" s="24"/>
-      <c r="C55" s="24"/>
-      <c r="D55" s="24"/>
-      <c r="E55" s="24"/>
-      <c r="F55" s="24"/>
-      <c r="G55" s="24"/>
-      <c r="H55" s="24"/>
+      <c r="A55" s="27"/>
+      <c r="B55" s="27"/>
+      <c r="C55" s="27"/>
+      <c r="D55" s="27"/>
+      <c r="E55" s="27"/>
+      <c r="F55" s="27"/>
+      <c r="G55" s="27"/>
+      <c r="H55" s="27"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56" s="24"/>
-      <c r="B56" s="24"/>
-      <c r="C56" s="24"/>
-      <c r="D56" s="24"/>
-      <c r="E56" s="24"/>
-      <c r="F56" s="24"/>
-      <c r="G56" s="24"/>
-      <c r="H56" s="24"/>
+      <c r="A56" s="27"/>
+      <c r="B56" s="27"/>
+      <c r="C56" s="27"/>
+      <c r="D56" s="27"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="27"/>
+      <c r="H56" s="27"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57" s="24"/>
-      <c r="B57" s="24"/>
-      <c r="C57" s="24"/>
-      <c r="D57" s="24"/>
-      <c r="E57" s="24"/>
-      <c r="F57" s="24"/>
-      <c r="G57" s="24"/>
-      <c r="H57" s="24"/>
+      <c r="A57" s="27"/>
+      <c r="B57" s="27"/>
+      <c r="C57" s="27"/>
+      <c r="D57" s="27"/>
+      <c r="E57" s="27"/>
+      <c r="F57" s="27"/>
+      <c r="G57" s="27"/>
+      <c r="H57" s="27"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" s="24"/>
-      <c r="B58" s="24"/>
-      <c r="C58" s="24"/>
-      <c r="D58" s="24"/>
-      <c r="E58" s="24"/>
-      <c r="F58" s="24"/>
-      <c r="G58" s="24"/>
-      <c r="H58" s="24"/>
+      <c r="A58" s="27"/>
+      <c r="B58" s="27"/>
+      <c r="C58" s="27"/>
+      <c r="D58" s="27"/>
+      <c r="E58" s="27"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="27"/>
+      <c r="H58" s="27"/>
     </row>
     <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="24"/>
-      <c r="B59" s="24"/>
-      <c r="C59" s="24"/>
-      <c r="D59" s="24"/>
-      <c r="E59" s="24"/>
-      <c r="F59" s="24"/>
-      <c r="G59" s="24"/>
-      <c r="H59" s="24"/>
+      <c r="A59" s="27"/>
+      <c r="B59" s="27"/>
+      <c r="C59" s="27"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="27"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="27"/>
+      <c r="H59" s="27"/>
     </row>
     <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="17"/>
@@ -1671,254 +1661,254 @@
       <c r="H60" s="17"/>
     </row>
     <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="24"/>
-      <c r="B61" s="24"/>
-      <c r="C61" s="24"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="24"/>
+      <c r="A61" s="27"/>
+      <c r="B61" s="27"/>
+      <c r="C61" s="27"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="27"/>
+      <c r="F61" s="27"/>
+      <c r="G61" s="27"/>
+      <c r="H61" s="27"/>
     </row>
     <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="24"/>
-      <c r="B62" s="24"/>
-      <c r="C62" s="24"/>
-      <c r="D62" s="24"/>
-      <c r="E62" s="24"/>
-      <c r="F62" s="24"/>
-      <c r="G62" s="24"/>
-      <c r="H62" s="24"/>
+      <c r="A62" s="27"/>
+      <c r="B62" s="27"/>
+      <c r="C62" s="27"/>
+      <c r="D62" s="27"/>
+      <c r="E62" s="27"/>
+      <c r="F62" s="27"/>
+      <c r="G62" s="27"/>
+      <c r="H62" s="27"/>
     </row>
     <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="24"/>
-      <c r="B63" s="24"/>
-      <c r="C63" s="24"/>
-      <c r="D63" s="24"/>
-      <c r="E63" s="24"/>
-      <c r="F63" s="24"/>
-      <c r="G63" s="24"/>
-      <c r="H63" s="24"/>
+      <c r="A63" s="27"/>
+      <c r="B63" s="27"/>
+      <c r="C63" s="27"/>
+      <c r="D63" s="27"/>
+      <c r="E63" s="27"/>
+      <c r="F63" s="27"/>
+      <c r="G63" s="27"/>
+      <c r="H63" s="27"/>
     </row>
     <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="24"/>
-      <c r="B64" s="24"/>
-      <c r="C64" s="24"/>
-      <c r="D64" s="24"/>
-      <c r="E64" s="24"/>
-      <c r="F64" s="24"/>
-      <c r="G64" s="24"/>
-      <c r="H64" s="24"/>
+      <c r="A64" s="27"/>
+      <c r="B64" s="27"/>
+      <c r="C64" s="27"/>
+      <c r="D64" s="27"/>
+      <c r="E64" s="27"/>
+      <c r="F64" s="27"/>
+      <c r="G64" s="27"/>
+      <c r="H64" s="27"/>
     </row>
     <row r="65" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="24"/>
-      <c r="B65" s="24"/>
-      <c r="C65" s="24"/>
-      <c r="D65" s="24"/>
-      <c r="E65" s="24"/>
-      <c r="F65" s="24"/>
-      <c r="G65" s="24"/>
-      <c r="H65" s="24"/>
+      <c r="A65" s="27"/>
+      <c r="B65" s="27"/>
+      <c r="C65" s="27"/>
+      <c r="D65" s="27"/>
+      <c r="E65" s="27"/>
+      <c r="F65" s="27"/>
+      <c r="G65" s="27"/>
+      <c r="H65" s="27"/>
     </row>
     <row r="66" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="24"/>
-      <c r="B66" s="24"/>
-      <c r="C66" s="24"/>
-      <c r="D66" s="24"/>
-      <c r="E66" s="24"/>
-      <c r="F66" s="24"/>
-      <c r="G66" s="24"/>
-      <c r="H66" s="24"/>
+      <c r="A66" s="27"/>
+      <c r="B66" s="27"/>
+      <c r="C66" s="27"/>
+      <c r="D66" s="27"/>
+      <c r="E66" s="27"/>
+      <c r="F66" s="27"/>
+      <c r="G66" s="27"/>
+      <c r="H66" s="27"/>
     </row>
     <row r="67" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="24"/>
-      <c r="B67" s="24"/>
-      <c r="C67" s="24"/>
-      <c r="D67" s="24"/>
-      <c r="E67" s="24"/>
-      <c r="F67" s="24"/>
-      <c r="G67" s="24"/>
-      <c r="H67" s="24"/>
+      <c r="A67" s="27"/>
+      <c r="B67" s="27"/>
+      <c r="C67" s="27"/>
+      <c r="D67" s="27"/>
+      <c r="E67" s="27"/>
+      <c r="F67" s="27"/>
+      <c r="G67" s="27"/>
+      <c r="H67" s="27"/>
     </row>
     <row r="68" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="24"/>
-      <c r="B68" s="24"/>
-      <c r="C68" s="24"/>
-      <c r="D68" s="24"/>
-      <c r="E68" s="24"/>
-      <c r="F68" s="24"/>
-      <c r="G68" s="24"/>
-      <c r="H68" s="24"/>
+      <c r="A68" s="27"/>
+      <c r="B68" s="27"/>
+      <c r="C68" s="27"/>
+      <c r="D68" s="27"/>
+      <c r="E68" s="27"/>
+      <c r="F68" s="27"/>
+      <c r="G68" s="27"/>
+      <c r="H68" s="27"/>
     </row>
     <row r="69" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="24"/>
-      <c r="B69" s="24"/>
-      <c r="C69" s="24"/>
-      <c r="D69" s="24"/>
-      <c r="E69" s="24"/>
-      <c r="F69" s="24"/>
-      <c r="G69" s="24"/>
-      <c r="H69" s="24"/>
+      <c r="A69" s="27"/>
+      <c r="B69" s="27"/>
+      <c r="C69" s="27"/>
+      <c r="D69" s="27"/>
+      <c r="E69" s="27"/>
+      <c r="F69" s="27"/>
+      <c r="G69" s="27"/>
+      <c r="H69" s="27"/>
     </row>
     <row r="70" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="24"/>
-      <c r="B70" s="24"/>
-      <c r="C70" s="24"/>
-      <c r="D70" s="24"/>
-      <c r="E70" s="24"/>
-      <c r="F70" s="24"/>
-      <c r="G70" s="24"/>
-      <c r="H70" s="24"/>
+      <c r="A70" s="27"/>
+      <c r="B70" s="27"/>
+      <c r="C70" s="27"/>
+      <c r="D70" s="27"/>
+      <c r="E70" s="27"/>
+      <c r="F70" s="27"/>
+      <c r="G70" s="27"/>
+      <c r="H70" s="27"/>
     </row>
     <row r="71" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="24"/>
-      <c r="B71" s="24"/>
-      <c r="C71" s="24"/>
-      <c r="D71" s="24"/>
-      <c r="E71" s="24"/>
-      <c r="F71" s="24"/>
-      <c r="G71" s="24"/>
-      <c r="H71" s="24"/>
+      <c r="A71" s="27"/>
+      <c r="B71" s="27"/>
+      <c r="C71" s="27"/>
+      <c r="D71" s="27"/>
+      <c r="E71" s="27"/>
+      <c r="F71" s="27"/>
+      <c r="G71" s="27"/>
+      <c r="H71" s="27"/>
     </row>
     <row r="72" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="24"/>
-      <c r="B72" s="24"/>
-      <c r="C72" s="24"/>
-      <c r="D72" s="24"/>
-      <c r="E72" s="24"/>
-      <c r="F72" s="24"/>
-      <c r="G72" s="24"/>
-      <c r="H72" s="24"/>
+      <c r="A72" s="27"/>
+      <c r="B72" s="27"/>
+      <c r="C72" s="27"/>
+      <c r="D72" s="27"/>
+      <c r="E72" s="27"/>
+      <c r="F72" s="27"/>
+      <c r="G72" s="27"/>
+      <c r="H72" s="27"/>
     </row>
     <row r="73" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="24"/>
-      <c r="B73" s="24"/>
-      <c r="C73" s="24"/>
-      <c r="D73" s="24"/>
-      <c r="E73" s="24"/>
-      <c r="F73" s="24"/>
-      <c r="G73" s="24"/>
-      <c r="H73" s="24"/>
+      <c r="A73" s="27"/>
+      <c r="B73" s="27"/>
+      <c r="C73" s="27"/>
+      <c r="D73" s="27"/>
+      <c r="E73" s="27"/>
+      <c r="F73" s="27"/>
+      <c r="G73" s="27"/>
+      <c r="H73" s="27"/>
     </row>
     <row r="74" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="24"/>
-      <c r="B74" s="24"/>
-      <c r="C74" s="24"/>
-      <c r="D74" s="24"/>
-      <c r="E74" s="24"/>
-      <c r="F74" s="24"/>
-      <c r="G74" s="24"/>
-      <c r="H74" s="24"/>
+      <c r="A74" s="27"/>
+      <c r="B74" s="27"/>
+      <c r="C74" s="27"/>
+      <c r="D74" s="27"/>
+      <c r="E74" s="27"/>
+      <c r="F74" s="27"/>
+      <c r="G74" s="27"/>
+      <c r="H74" s="27"/>
     </row>
     <row r="75" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="24"/>
-      <c r="B75" s="24"/>
-      <c r="C75" s="24"/>
-      <c r="D75" s="24"/>
-      <c r="E75" s="24"/>
-      <c r="F75" s="24"/>
-      <c r="G75" s="24"/>
-      <c r="H75" s="24"/>
+      <c r="A75" s="27"/>
+      <c r="B75" s="27"/>
+      <c r="C75" s="27"/>
+      <c r="D75" s="27"/>
+      <c r="E75" s="27"/>
+      <c r="F75" s="27"/>
+      <c r="G75" s="27"/>
+      <c r="H75" s="27"/>
     </row>
     <row r="76" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="24"/>
-      <c r="B76" s="24"/>
-      <c r="C76" s="24"/>
-      <c r="D76" s="24"/>
-      <c r="E76" s="24"/>
-      <c r="F76" s="24"/>
-      <c r="G76" s="24"/>
-      <c r="H76" s="24"/>
+      <c r="A76" s="27"/>
+      <c r="B76" s="27"/>
+      <c r="C76" s="27"/>
+      <c r="D76" s="27"/>
+      <c r="E76" s="27"/>
+      <c r="F76" s="27"/>
+      <c r="G76" s="27"/>
+      <c r="H76" s="27"/>
     </row>
     <row r="77" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="24"/>
-      <c r="B77" s="24"/>
-      <c r="C77" s="24"/>
-      <c r="D77" s="24"/>
-      <c r="E77" s="24"/>
-      <c r="F77" s="24"/>
-      <c r="G77" s="24"/>
-      <c r="H77" s="24"/>
+      <c r="A77" s="27"/>
+      <c r="B77" s="27"/>
+      <c r="C77" s="27"/>
+      <c r="D77" s="27"/>
+      <c r="E77" s="27"/>
+      <c r="F77" s="27"/>
+      <c r="G77" s="27"/>
+      <c r="H77" s="27"/>
     </row>
     <row r="78" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="24"/>
-      <c r="B78" s="24"/>
-      <c r="C78" s="24"/>
-      <c r="D78" s="24"/>
-      <c r="E78" s="24"/>
-      <c r="F78" s="24"/>
-      <c r="G78" s="24"/>
-      <c r="H78" s="24"/>
+      <c r="A78" s="27"/>
+      <c r="B78" s="27"/>
+      <c r="C78" s="27"/>
+      <c r="D78" s="27"/>
+      <c r="E78" s="27"/>
+      <c r="F78" s="27"/>
+      <c r="G78" s="27"/>
+      <c r="H78" s="27"/>
     </row>
     <row r="79" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="24"/>
-      <c r="B79" s="24"/>
-      <c r="C79" s="24"/>
-      <c r="D79" s="24"/>
-      <c r="E79" s="24"/>
-      <c r="F79" s="24"/>
-      <c r="G79" s="24"/>
-      <c r="H79" s="24"/>
+      <c r="A79" s="27"/>
+      <c r="B79" s="27"/>
+      <c r="C79" s="27"/>
+      <c r="D79" s="27"/>
+      <c r="E79" s="27"/>
+      <c r="F79" s="27"/>
+      <c r="G79" s="27"/>
+      <c r="H79" s="27"/>
     </row>
     <row r="80" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="24"/>
-      <c r="B80" s="24"/>
-      <c r="C80" s="24"/>
-      <c r="D80" s="24"/>
-      <c r="E80" s="24"/>
-      <c r="F80" s="24"/>
-      <c r="G80" s="24"/>
-      <c r="H80" s="24"/>
+      <c r="A80" s="27"/>
+      <c r="B80" s="27"/>
+      <c r="C80" s="27"/>
+      <c r="D80" s="27"/>
+      <c r="E80" s="27"/>
+      <c r="F80" s="27"/>
+      <c r="G80" s="27"/>
+      <c r="H80" s="27"/>
     </row>
     <row r="81" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="24"/>
-      <c r="B81" s="24"/>
-      <c r="C81" s="24"/>
-      <c r="D81" s="24"/>
-      <c r="E81" s="24"/>
-      <c r="F81" s="24"/>
-      <c r="G81" s="24"/>
-      <c r="H81" s="24"/>
+      <c r="A81" s="27"/>
+      <c r="B81" s="27"/>
+      <c r="C81" s="27"/>
+      <c r="D81" s="27"/>
+      <c r="E81" s="27"/>
+      <c r="F81" s="27"/>
+      <c r="G81" s="27"/>
+      <c r="H81" s="27"/>
     </row>
     <row r="82" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="24"/>
-      <c r="B82" s="24"/>
-      <c r="C82" s="24"/>
-      <c r="D82" s="24"/>
-      <c r="E82" s="24"/>
-      <c r="F82" s="24"/>
-      <c r="G82" s="24"/>
-      <c r="H82" s="24"/>
+      <c r="A82" s="27"/>
+      <c r="B82" s="27"/>
+      <c r="C82" s="27"/>
+      <c r="D82" s="27"/>
+      <c r="E82" s="27"/>
+      <c r="F82" s="27"/>
+      <c r="G82" s="27"/>
+      <c r="H82" s="27"/>
     </row>
     <row r="83" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="24"/>
-      <c r="B83" s="24"/>
-      <c r="C83" s="24"/>
-      <c r="D83" s="24"/>
-      <c r="E83" s="24"/>
-      <c r="F83" s="24"/>
-      <c r="G83" s="24"/>
-      <c r="H83" s="24"/>
+      <c r="A83" s="27"/>
+      <c r="B83" s="27"/>
+      <c r="C83" s="27"/>
+      <c r="D83" s="27"/>
+      <c r="E83" s="27"/>
+      <c r="F83" s="27"/>
+      <c r="G83" s="27"/>
+      <c r="H83" s="27"/>
     </row>
     <row r="84" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="24"/>
-      <c r="B84" s="24"/>
-      <c r="C84" s="24"/>
-      <c r="D84" s="24"/>
-      <c r="E84" s="24"/>
-      <c r="F84" s="24"/>
-      <c r="G84" s="24"/>
-      <c r="H84" s="24"/>
+      <c r="A84" s="27"/>
+      <c r="B84" s="27"/>
+      <c r="C84" s="27"/>
+      <c r="D84" s="27"/>
+      <c r="E84" s="27"/>
+      <c r="F84" s="27"/>
+      <c r="G84" s="27"/>
+      <c r="H84" s="27"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A85" s="24"/>
-      <c r="B85" s="24"/>
-      <c r="C85" s="24"/>
-      <c r="D85" s="24"/>
-      <c r="E85" s="24"/>
-      <c r="F85" s="24"/>
-      <c r="G85" s="24"/>
-      <c r="H85" s="24"/>
+      <c r="A85" s="27"/>
+      <c r="B85" s="27"/>
+      <c r="C85" s="27"/>
+      <c r="D85" s="27"/>
+      <c r="E85" s="27"/>
+      <c r="F85" s="27"/>
+      <c r="G85" s="27"/>
+      <c r="H85" s="27"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="17"/>
@@ -1931,278 +1921,254 @@
       <c r="H86" s="17"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A87" s="24"/>
-      <c r="B87" s="24"/>
-      <c r="C87" s="24"/>
-      <c r="D87" s="24"/>
-      <c r="E87" s="24"/>
-      <c r="F87" s="24"/>
-      <c r="G87" s="24"/>
-      <c r="H87" s="24"/>
+      <c r="A87" s="27"/>
+      <c r="B87" s="27"/>
+      <c r="C87" s="27"/>
+      <c r="D87" s="27"/>
+      <c r="E87" s="27"/>
+      <c r="F87" s="27"/>
+      <c r="G87" s="27"/>
+      <c r="H87" s="27"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A88" s="24"/>
-      <c r="B88" s="24"/>
-      <c r="C88" s="24"/>
-      <c r="D88" s="24"/>
-      <c r="E88" s="24"/>
-      <c r="F88" s="24"/>
-      <c r="G88" s="24"/>
-      <c r="H88" s="24"/>
+      <c r="A88" s="27"/>
+      <c r="B88" s="27"/>
+      <c r="C88" s="27"/>
+      <c r="D88" s="27"/>
+      <c r="E88" s="27"/>
+      <c r="F88" s="27"/>
+      <c r="G88" s="27"/>
+      <c r="H88" s="27"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A89" s="24"/>
-      <c r="B89" s="24"/>
-      <c r="C89" s="24"/>
-      <c r="D89" s="24"/>
-      <c r="E89" s="24"/>
-      <c r="F89" s="24"/>
-      <c r="G89" s="24"/>
-      <c r="H89" s="24"/>
+      <c r="A89" s="27"/>
+      <c r="B89" s="27"/>
+      <c r="C89" s="27"/>
+      <c r="D89" s="27"/>
+      <c r="E89" s="27"/>
+      <c r="F89" s="27"/>
+      <c r="G89" s="27"/>
+      <c r="H89" s="27"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A90" s="24"/>
-      <c r="B90" s="24"/>
-      <c r="C90" s="24"/>
-      <c r="D90" s="24"/>
-      <c r="E90" s="24"/>
-      <c r="F90" s="24"/>
-      <c r="G90" s="24"/>
-      <c r="H90" s="24"/>
+      <c r="A90" s="27"/>
+      <c r="B90" s="27"/>
+      <c r="C90" s="27"/>
+      <c r="D90" s="27"/>
+      <c r="E90" s="27"/>
+      <c r="F90" s="27"/>
+      <c r="G90" s="27"/>
+      <c r="H90" s="27"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A91" s="24"/>
-      <c r="B91" s="24"/>
-      <c r="C91" s="24"/>
-      <c r="D91" s="24"/>
-      <c r="E91" s="24"/>
-      <c r="F91" s="24"/>
-      <c r="G91" s="24"/>
-      <c r="H91" s="24"/>
+      <c r="A91" s="27"/>
+      <c r="B91" s="27"/>
+      <c r="C91" s="27"/>
+      <c r="D91" s="27"/>
+      <c r="E91" s="27"/>
+      <c r="F91" s="27"/>
+      <c r="G91" s="27"/>
+      <c r="H91" s="27"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A92" s="24"/>
-      <c r="B92" s="24"/>
-      <c r="C92" s="24"/>
-      <c r="D92" s="24"/>
-      <c r="E92" s="24"/>
-      <c r="F92" s="24"/>
-      <c r="G92" s="24"/>
-      <c r="H92" s="24"/>
+      <c r="A92" s="27"/>
+      <c r="B92" s="27"/>
+      <c r="C92" s="27"/>
+      <c r="D92" s="27"/>
+      <c r="E92" s="27"/>
+      <c r="F92" s="27"/>
+      <c r="G92" s="27"/>
+      <c r="H92" s="27"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A93" s="24"/>
-      <c r="B93" s="24"/>
-      <c r="C93" s="24"/>
-      <c r="D93" s="24"/>
-      <c r="E93" s="24"/>
-      <c r="F93" s="24"/>
-      <c r="G93" s="24"/>
-      <c r="H93" s="24"/>
+      <c r="A93" s="27"/>
+      <c r="B93" s="27"/>
+      <c r="C93" s="27"/>
+      <c r="D93" s="27"/>
+      <c r="E93" s="27"/>
+      <c r="F93" s="27"/>
+      <c r="G93" s="27"/>
+      <c r="H93" s="27"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A94" s="24"/>
-      <c r="B94" s="24"/>
-      <c r="C94" s="24"/>
-      <c r="D94" s="24"/>
-      <c r="E94" s="24"/>
-      <c r="F94" s="24"/>
-      <c r="G94" s="24"/>
-      <c r="H94" s="24"/>
+      <c r="A94" s="27"/>
+      <c r="B94" s="27"/>
+      <c r="C94" s="27"/>
+      <c r="D94" s="27"/>
+      <c r="E94" s="27"/>
+      <c r="F94" s="27"/>
+      <c r="G94" s="27"/>
+      <c r="H94" s="27"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A95" s="24"/>
-      <c r="B95" s="24"/>
-      <c r="C95" s="24"/>
-      <c r="D95" s="24"/>
-      <c r="E95" s="24"/>
-      <c r="F95" s="24"/>
-      <c r="G95" s="24"/>
-      <c r="H95" s="24"/>
+      <c r="A95" s="27"/>
+      <c r="B95" s="27"/>
+      <c r="C95" s="27"/>
+      <c r="D95" s="27"/>
+      <c r="E95" s="27"/>
+      <c r="F95" s="27"/>
+      <c r="G95" s="27"/>
+      <c r="H95" s="27"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A96" s="24"/>
-      <c r="B96" s="24"/>
-      <c r="C96" s="24"/>
-      <c r="D96" s="24"/>
-      <c r="E96" s="24"/>
-      <c r="F96" s="24"/>
-      <c r="G96" s="24"/>
-      <c r="H96" s="24"/>
+      <c r="A96" s="27"/>
+      <c r="B96" s="27"/>
+      <c r="C96" s="27"/>
+      <c r="D96" s="27"/>
+      <c r="E96" s="27"/>
+      <c r="F96" s="27"/>
+      <c r="G96" s="27"/>
+      <c r="H96" s="27"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A97" s="24"/>
-      <c r="B97" s="24"/>
-      <c r="C97" s="24"/>
-      <c r="D97" s="24"/>
-      <c r="E97" s="24"/>
-      <c r="F97" s="24"/>
-      <c r="G97" s="24"/>
-      <c r="H97" s="24"/>
+      <c r="A97" s="27"/>
+      <c r="B97" s="27"/>
+      <c r="C97" s="27"/>
+      <c r="D97" s="27"/>
+      <c r="E97" s="27"/>
+      <c r="F97" s="27"/>
+      <c r="G97" s="27"/>
+      <c r="H97" s="27"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A98" s="24"/>
-      <c r="B98" s="24"/>
-      <c r="C98" s="24"/>
-      <c r="D98" s="24"/>
-      <c r="E98" s="24"/>
-      <c r="F98" s="24"/>
-      <c r="G98" s="24"/>
-      <c r="H98" s="24"/>
+      <c r="A98" s="27"/>
+      <c r="B98" s="27"/>
+      <c r="C98" s="27"/>
+      <c r="D98" s="27"/>
+      <c r="E98" s="27"/>
+      <c r="F98" s="27"/>
+      <c r="G98" s="27"/>
+      <c r="H98" s="27"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A99" s="24"/>
-      <c r="B99" s="24"/>
-      <c r="C99" s="24"/>
-      <c r="D99" s="24"/>
-      <c r="E99" s="24"/>
-      <c r="F99" s="24"/>
-      <c r="G99" s="24"/>
-      <c r="H99" s="24"/>
+      <c r="A99" s="27"/>
+      <c r="B99" s="27"/>
+      <c r="C99" s="27"/>
+      <c r="D99" s="27"/>
+      <c r="E99" s="27"/>
+      <c r="F99" s="27"/>
+      <c r="G99" s="27"/>
+      <c r="H99" s="27"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A100" s="24"/>
-      <c r="B100" s="24"/>
-      <c r="C100" s="24"/>
-      <c r="D100" s="24"/>
-      <c r="E100" s="24"/>
-      <c r="F100" s="24"/>
-      <c r="G100" s="24"/>
-      <c r="H100" s="24"/>
+      <c r="A100" s="27"/>
+      <c r="B100" s="27"/>
+      <c r="C100" s="27"/>
+      <c r="D100" s="27"/>
+      <c r="E100" s="27"/>
+      <c r="F100" s="27"/>
+      <c r="G100" s="27"/>
+      <c r="H100" s="27"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A101" s="24"/>
-      <c r="B101" s="24"/>
-      <c r="C101" s="24"/>
-      <c r="D101" s="24"/>
-      <c r="E101" s="24"/>
-      <c r="F101" s="24"/>
-      <c r="G101" s="24"/>
-      <c r="H101" s="24"/>
+      <c r="A101" s="27"/>
+      <c r="B101" s="27"/>
+      <c r="C101" s="27"/>
+      <c r="D101" s="27"/>
+      <c r="E101" s="27"/>
+      <c r="F101" s="27"/>
+      <c r="G101" s="27"/>
+      <c r="H101" s="27"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A102" s="24"/>
-      <c r="B102" s="24"/>
-      <c r="C102" s="24"/>
-      <c r="D102" s="24"/>
-      <c r="E102" s="24"/>
-      <c r="F102" s="24"/>
-      <c r="G102" s="24"/>
-      <c r="H102" s="24"/>
+      <c r="A102" s="27"/>
+      <c r="B102" s="27"/>
+      <c r="C102" s="27"/>
+      <c r="D102" s="27"/>
+      <c r="E102" s="27"/>
+      <c r="F102" s="27"/>
+      <c r="G102" s="27"/>
+      <c r="H102" s="27"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A103" s="24"/>
-      <c r="B103" s="24"/>
-      <c r="C103" s="24"/>
-      <c r="D103" s="24"/>
-      <c r="E103" s="24"/>
-      <c r="F103" s="24"/>
-      <c r="G103" s="24"/>
-      <c r="H103" s="24"/>
+      <c r="A103" s="27"/>
+      <c r="B103" s="27"/>
+      <c r="C103" s="27"/>
+      <c r="D103" s="27"/>
+      <c r="E103" s="27"/>
+      <c r="F103" s="27"/>
+      <c r="G103" s="27"/>
+      <c r="H103" s="27"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A104" s="24"/>
-      <c r="B104" s="24"/>
-      <c r="C104" s="24"/>
-      <c r="D104" s="24"/>
-      <c r="E104" s="24"/>
-      <c r="F104" s="24"/>
-      <c r="G104" s="24"/>
-      <c r="H104" s="24"/>
+      <c r="A104" s="27"/>
+      <c r="B104" s="27"/>
+      <c r="C104" s="27"/>
+      <c r="D104" s="27"/>
+      <c r="E104" s="27"/>
+      <c r="F104" s="27"/>
+      <c r="G104" s="27"/>
+      <c r="H104" s="27"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A105" s="24"/>
-      <c r="B105" s="24"/>
-      <c r="C105" s="24"/>
-      <c r="D105" s="24"/>
-      <c r="E105" s="24"/>
-      <c r="F105" s="24"/>
-      <c r="G105" s="24"/>
-      <c r="H105" s="24"/>
+      <c r="A105" s="27"/>
+      <c r="B105" s="27"/>
+      <c r="C105" s="27"/>
+      <c r="D105" s="27"/>
+      <c r="E105" s="27"/>
+      <c r="F105" s="27"/>
+      <c r="G105" s="27"/>
+      <c r="H105" s="27"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A106" s="24"/>
-      <c r="B106" s="24"/>
-      <c r="C106" s="24"/>
-      <c r="D106" s="24"/>
-      <c r="E106" s="24"/>
-      <c r="F106" s="24"/>
-      <c r="G106" s="24"/>
-      <c r="H106" s="24"/>
+      <c r="A106" s="27"/>
+      <c r="B106" s="27"/>
+      <c r="C106" s="27"/>
+      <c r="D106" s="27"/>
+      <c r="E106" s="27"/>
+      <c r="F106" s="27"/>
+      <c r="G106" s="27"/>
+      <c r="H106" s="27"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A107" s="24"/>
-      <c r="B107" s="24"/>
-      <c r="C107" s="24"/>
-      <c r="D107" s="24"/>
-      <c r="E107" s="24"/>
-      <c r="F107" s="24"/>
-      <c r="G107" s="24"/>
-      <c r="H107" s="24"/>
+      <c r="A107" s="27"/>
+      <c r="B107" s="27"/>
+      <c r="C107" s="27"/>
+      <c r="D107" s="27"/>
+      <c r="E107" s="27"/>
+      <c r="F107" s="27"/>
+      <c r="G107" s="27"/>
+      <c r="H107" s="27"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A108" s="24"/>
-      <c r="B108" s="24"/>
-      <c r="C108" s="24"/>
-      <c r="D108" s="24"/>
-      <c r="E108" s="24"/>
-      <c r="F108" s="24"/>
-      <c r="G108" s="24"/>
-      <c r="H108" s="24"/>
+      <c r="A108" s="27"/>
+      <c r="B108" s="27"/>
+      <c r="C108" s="27"/>
+      <c r="D108" s="27"/>
+      <c r="E108" s="27"/>
+      <c r="F108" s="27"/>
+      <c r="G108" s="27"/>
+      <c r="H108" s="27"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A109" s="24"/>
-      <c r="B109" s="24"/>
-      <c r="C109" s="24"/>
-      <c r="D109" s="24"/>
-      <c r="E109" s="24"/>
-      <c r="F109" s="24"/>
-      <c r="G109" s="24"/>
-      <c r="H109" s="24"/>
+      <c r="A109" s="27"/>
+      <c r="B109" s="27"/>
+      <c r="C109" s="27"/>
+      <c r="D109" s="27"/>
+      <c r="E109" s="27"/>
+      <c r="F109" s="27"/>
+      <c r="G109" s="27"/>
+      <c r="H109" s="27"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A110" s="24"/>
-      <c r="B110" s="24"/>
-      <c r="C110" s="24"/>
-      <c r="D110" s="24"/>
-      <c r="E110" s="24"/>
-      <c r="F110" s="24"/>
-      <c r="G110" s="24"/>
-      <c r="H110" s="24"/>
+      <c r="A110" s="27"/>
+      <c r="B110" s="27"/>
+      <c r="C110" s="27"/>
+      <c r="D110" s="27"/>
+      <c r="E110" s="27"/>
+      <c r="F110" s="27"/>
+      <c r="G110" s="27"/>
+      <c r="H110" s="27"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A111" s="24"/>
-      <c r="B111" s="24"/>
-      <c r="C111" s="24"/>
-      <c r="D111" s="24"/>
-      <c r="E111" s="24"/>
-      <c r="F111" s="24"/>
-      <c r="G111" s="24"/>
-      <c r="H111" s="24"/>
-    </row>
-    <row r="112" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="23"/>
-      <c r="B112" s="23"/>
-      <c r="C112" s="23"/>
-      <c r="D112" s="23"/>
-      <c r="E112" s="23"/>
-      <c r="F112" s="23"/>
-      <c r="G112" s="23"/>
-      <c r="H112" s="23"/>
-    </row>
-    <row r="114" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C114" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D114" s="20"/>
-      <c r="E114" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F114" s="21"/>
-      <c r="G114" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="H114" s="22"/>
+      <c r="A111" s="27"/>
+      <c r="B111" s="27"/>
+      <c r="C111" s="27"/>
+      <c r="D111" s="27"/>
+      <c r="E111" s="27"/>
+      <c r="F111" s="27"/>
+      <c r="G111" s="27"/>
+      <c r="H111" s="27"/>
     </row>
     <row r="139" spans="17:23" x14ac:dyDescent="0.2">
       <c r="Q139" s="18"/>
@@ -2211,11 +2177,7 @@
       <c r="W139" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A112:H112"/>
-    <mergeCell ref="A36:H59"/>
-    <mergeCell ref="A61:H85"/>
-    <mergeCell ref="A87:H111"/>
+  <mergeCells count="4">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A6:H6"/>
@@ -2223,6 +2185,6 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="88" fitToHeight="2" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="88" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>